--- a/test_data/pro_gripper.xlsx
+++ b/test_data/pro_gripper.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10500" tabRatio="620" firstSheet="30" activeTab="36"/>
+    <workbookView windowWidth="27945" windowHeight="14055" tabRatio="620" firstSheet="31" activeTab="38"/>
   </bookViews>
   <sheets>
     <sheet name="get_firmware_version" sheetId="1" r:id="rId1"/>
@@ -1357,7 +1357,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
@@ -1380,7 +1380,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="28.8" spans="1:5">
+    <row r="2" ht="27" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1405,10 +1405,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.4444444444444" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.4416666666667" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1450,7 +1450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="27" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1467,7 +1467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="40.5" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="43.2" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="40.5" spans="1:6">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1511,13 +1511,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.5555555555556" customWidth="1"/>
-    <col min="2" max="2" width="27.1111111111111" customWidth="1"/>
-    <col min="3" max="3" width="24.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="13.4444444444444" customWidth="1"/>
-    <col min="5" max="5" width="13.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="13.5583333333333" customWidth="1"/>
+    <col min="2" max="2" width="27.1083333333333" customWidth="1"/>
+    <col min="3" max="3" width="24.5583333333333" customWidth="1"/>
+    <col min="4" max="4" width="13.4416666666667" customWidth="1"/>
+    <col min="5" max="5" width="13.225" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1562,13 +1562,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.5555555555556" customWidth="1"/>
-    <col min="2" max="2" width="27.1111111111111" customWidth="1"/>
-    <col min="3" max="3" width="24.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="13.4444444444444" customWidth="1"/>
-    <col min="5" max="5" width="13.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="13.5583333333333" customWidth="1"/>
+    <col min="2" max="2" width="27.1083333333333" customWidth="1"/>
+    <col min="3" max="3" width="24.5583333333333" customWidth="1"/>
+    <col min="4" max="4" width="13.4416666666667" customWidth="1"/>
+    <col min="5" max="5" width="13.225" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1655,13 +1655,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.5555555555556" customWidth="1"/>
-    <col min="2" max="2" width="27.1111111111111" customWidth="1"/>
-    <col min="3" max="3" width="24.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="13.4444444444444" customWidth="1"/>
-    <col min="5" max="5" width="13.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="13.5583333333333" customWidth="1"/>
+    <col min="2" max="2" width="27.1083333333333" customWidth="1"/>
+    <col min="3" max="3" width="24.5583333333333" customWidth="1"/>
+    <col min="4" max="4" width="13.4416666666667" customWidth="1"/>
+    <col min="5" max="5" width="13.225" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1748,13 +1748,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="19.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="19.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:5">
+    <row r="1" ht="27" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1796,13 +1796,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.5555555555556" customWidth="1"/>
-    <col min="2" max="2" width="27.1111111111111" customWidth="1"/>
-    <col min="3" max="3" width="24.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="13.4444444444444" customWidth="1"/>
-    <col min="5" max="5" width="13.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="13.5583333333333" customWidth="1"/>
+    <col min="2" max="2" width="27.1083333333333" customWidth="1"/>
+    <col min="3" max="3" width="24.5583333333333" customWidth="1"/>
+    <col min="4" max="4" width="13.4416666666667" customWidth="1"/>
+    <col min="5" max="5" width="13.225" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1889,13 +1889,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="19.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="19.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:5">
+    <row r="1" ht="27" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1937,13 +1937,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="19.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="19.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:5">
+    <row r="1" ht="27" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="28.8" spans="1:5">
+    <row r="2" ht="27" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1985,13 +1985,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="19.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="19.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:6">
+    <row r="1" ht="27" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="28.8" spans="1:6">
+    <row r="2" ht="27" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:6">
+    <row r="3" ht="27" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:6">
+    <row r="4" ht="27" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2075,13 +2075,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="19.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="19.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:6">
+    <row r="1" ht="27" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="28.8" spans="1:6">
+    <row r="2" ht="27" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2121,7 +2121,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:6">
+    <row r="3" ht="27" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:6">
+    <row r="4" ht="27" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2165,14 +2165,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="18.8888888888889" customWidth="1"/>
-    <col min="3" max="3" width="22.2222222222222" customWidth="1"/>
-    <col min="5" max="5" width="17.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="18.8916666666667" customWidth="1"/>
+    <col min="3" max="3" width="22.225" customWidth="1"/>
+    <col min="5" max="5" width="17.5583333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:5">
+    <row r="1" ht="27" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="28.8" spans="1:5">
+    <row r="2" ht="27" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2215,13 +2215,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="19.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="19.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:5">
+    <row r="1" ht="27" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2238,7 +2238,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="28.8" spans="1:5">
+    <row r="2" ht="27" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2263,15 +2263,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="1"/>
-    <col min="2" max="2" width="21.7777777777778" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="8.89166666666667" style="1"/>
+    <col min="2" max="2" width="21.775" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.775" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.89166666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:6">
+    <row r="1" ht="27" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="28.8" spans="1:6">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:6">
+    <row r="3" ht="27" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:6">
+    <row r="4" ht="27" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2355,13 +2355,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:5">
+    <row r="1" ht="27" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="28.8" spans="1:5">
+    <row r="2" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2403,15 +2403,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="1"/>
-    <col min="2" max="2" width="21.7777777777778" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="8.89166666666667" style="1"/>
+    <col min="2" max="2" width="21.775" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.775" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.89166666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="27" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="27" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2495,13 +2495,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:5">
+    <row r="1" ht="27" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2543,14 +2543,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
     <col min="6" max="6" width="11.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:6">
+    <row r="1" ht="27" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2694,14 +2694,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
     <col min="6" max="6" width="11.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:6">
+    <row r="1" ht="27" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="28.8" spans="1:6">
+    <row r="3" customFormat="1" ht="27" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="28.8" spans="1:6">
+    <row r="4" customFormat="1" ht="27" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2785,14 +2785,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
     <col min="6" max="6" width="11.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:6">
+    <row r="1" ht="27" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:6">
+    <row r="3" ht="27" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:6">
+    <row r="4" ht="27" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2876,17 +2876,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="1"/>
-    <col min="2" max="2" width="21.7777777777778" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" style="1" customWidth="1"/>
-    <col min="4" max="5" width="8.88888888888889" style="1"/>
-    <col min="6" max="6" width="12.7777777777778" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="8.89166666666667" style="1"/>
+    <col min="2" max="2" width="21.775" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.775" style="1" customWidth="1"/>
+    <col min="4" max="5" width="8.89166666666667" style="1"/>
+    <col min="6" max="6" width="12.775" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.89166666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:6">
+    <row r="1" ht="27" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2970,13 +2970,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:5">
+    <row r="1" ht="27" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3018,14 +3018,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="18.8888888888889" customWidth="1"/>
-    <col min="3" max="3" width="22.2222222222222" customWidth="1"/>
-    <col min="5" max="5" width="17.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="18.8916666666667" customWidth="1"/>
+    <col min="3" max="3" width="22.225" customWidth="1"/>
+    <col min="5" max="5" width="17.5583333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:5">
+    <row r="1" ht="27" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3068,13 +3068,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:5">
+    <row r="1" ht="27" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3116,13 +3116,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:5">
+    <row r="1" ht="27" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3164,17 +3164,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="1"/>
-    <col min="2" max="2" width="21.7777777777778" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" style="1" customWidth="1"/>
-    <col min="4" max="6" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="8.89166666666667" style="1"/>
+    <col min="2" max="2" width="21.775" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.775" style="1" customWidth="1"/>
+    <col min="4" max="6" width="8.89166666666667" style="1"/>
     <col min="7" max="7" width="12.6666666666667" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88888888888889" style="1"/>
+    <col min="8" max="16384" width="8.89166666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:7">
+    <row r="1" ht="27" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3217,7 +3217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:7">
+    <row r="3" ht="27" spans="1:7">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:7">
+    <row r="5" ht="27" spans="1:7">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -3271,7 +3271,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" ht="28.8" spans="1:7">
+    <row r="6" ht="27" spans="1:7">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -3301,13 +3301,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:5">
+    <row r="1" ht="27" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3349,13 +3349,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:5">
+    <row r="1" ht="27" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3397,13 +3397,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:5">
+    <row r="1" ht="27" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3445,13 +3445,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:5">
+    <row r="1" ht="27" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3493,15 +3493,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="1"/>
-    <col min="2" max="2" width="21.7777777777778" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="8.89166666666667" style="1"/>
+    <col min="2" max="2" width="21.775" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.775" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.89166666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:6">
+    <row r="1" ht="27" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:6">
+    <row r="3" ht="27" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:6">
+    <row r="4" ht="27" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3585,13 +3585,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:5">
+    <row r="1" ht="27" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3633,15 +3633,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="1"/>
-    <col min="2" max="2" width="21.7777777777778" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="8.89166666666667" style="1"/>
+    <col min="2" max="2" width="21.775" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.775" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.89166666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:6">
+    <row r="1" ht="27" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:6">
+    <row r="3" ht="27" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3698,7 +3698,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:6">
+    <row r="4" ht="27" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3725,10 +3725,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.225" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -3772,7 +3772,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:6">
+    <row r="3" ht="27" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3789,7 +3789,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:6">
+    <row r="4" ht="27" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3816,13 +3816,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:5">
+    <row r="1" ht="27" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3864,11 +3864,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="22.6666666666667" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="5" max="5" width="12.8888888888889" customWidth="1"/>
+    <col min="5" max="5" width="12.8916666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3913,10 +3913,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.225" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4004,17 +4004,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="1"/>
-    <col min="2" max="2" width="20.4444444444444" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.5555555555556" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7777777777778" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.2222222222222" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="8.89166666666667" style="1"/>
+    <col min="2" max="2" width="20.4416666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5583333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.775" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.225" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.89166666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:6">
+    <row r="1" ht="27" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="28.8" spans="1:6">
+    <row r="2" ht="27" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -4054,7 +4054,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:6">
+    <row r="3" ht="27" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -4074,7 +4074,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:6">
+    <row r="4" ht="27" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -4091,7 +4091,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:6">
+    <row r="5" ht="27" spans="1:6">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -4118,17 +4118,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.1111111111111" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.8888888888889" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.4444444444444" style="1" customWidth="1"/>
-    <col min="5" max="6" width="13.2222222222222" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.1083333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.8916666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.4416666666667" style="1" customWidth="1"/>
+    <col min="5" max="6" width="13.225" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.89166666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:7">
+    <row r="1" ht="27" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4197,7 +4197,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:7">
+    <row r="4" ht="27" spans="1:7">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -4217,7 +4217,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:7">
+    <row r="5" ht="27" spans="1:7">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -4247,13 +4247,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.5555555555556" customWidth="1"/>
-    <col min="2" max="2" width="27.1111111111111" customWidth="1"/>
-    <col min="3" max="3" width="24.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="13.4444444444444" customWidth="1"/>
-    <col min="5" max="5" width="13.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="13.5583333333333" customWidth="1"/>
+    <col min="2" max="2" width="27.1083333333333" customWidth="1"/>
+    <col min="3" max="3" width="24.5583333333333" customWidth="1"/>
+    <col min="4" max="4" width="13.4416666666667" customWidth="1"/>
+    <col min="5" max="5" width="13.225" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">

--- a/test_data/pro_gripper.xlsx
+++ b/test_data/pro_gripper.xlsx
@@ -4,24 +4,37 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="14055" firstSheet="3" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="12255" firstSheet="23" activeTab="24"/>
   </bookViews>
   <sheets>
-    <sheet name="get_pro_gripper" sheetId="1" r:id="rId1"/>
-    <sheet name="get_pro_gripper_angle" sheetId="2" r:id="rId2"/>
-    <sheet name="get_pro_gripper_speed" sheetId="3" r:id="rId3"/>
-    <sheet name="get_pro_gripper_status" sheetId="4" r:id="rId4"/>
-    <sheet name="set_pro_gripper" sheetId="5" r:id="rId5"/>
-    <sheet name="set_pro_gripper_abs_angle" sheetId="6" r:id="rId6"/>
-    <sheet name="set_pro_gripper_angle" sheetId="7" r:id="rId7"/>
-    <sheet name="set_pro_gripper_calibration" sheetId="8" r:id="rId8"/>
-    <sheet name="set_pro_gripper_close" sheetId="9" r:id="rId9"/>
-    <sheet name="set_pro_gripper_open" sheetId="10" r:id="rId10"/>
-    <sheet name="set_pro_gripper_pause" sheetId="11" r:id="rId11"/>
-    <sheet name="set_pro_gripper_resume" sheetId="12" r:id="rId12"/>
-    <sheet name="set_pro_gripper_speed" sheetId="13" r:id="rId13"/>
+    <sheet name="get_modified_version" sheetId="1" r:id="rId1"/>
+    <sheet name="get_firmware_version" sheetId="16" r:id="rId2"/>
+    <sheet name="get_pro_gripper_angle" sheetId="2" r:id="rId3"/>
+    <sheet name="get_pro_gripper_speed" sheetId="3" r:id="rId4"/>
+    <sheet name="get_pro_gripper_status" sheetId="4" r:id="rId5"/>
+    <sheet name="set_pro_gripper" sheetId="5" r:id="rId6"/>
+    <sheet name="set_pro_gripper_abs_angle" sheetId="6" r:id="rId7"/>
+    <sheet name="set_pro_gripper_angle" sheetId="7" r:id="rId8"/>
+    <sheet name="set_pro_gripper_calibration" sheetId="8" r:id="rId9"/>
+    <sheet name="set_pro_gripper_close" sheetId="9" r:id="rId10"/>
+    <sheet name="set_pro_gripper_open" sheetId="10" r:id="rId11"/>
+    <sheet name="set_pro_gripper_pause" sheetId="11" r:id="rId12"/>
+    <sheet name="set_pro_gripper_resume" sheetId="12" r:id="rId13"/>
     <sheet name="set_pro_gripper_stop" sheetId="14" r:id="rId14"/>
     <sheet name="set_pro_gripper_torque" sheetId="15" r:id="rId15"/>
+    <sheet name="get_pro_gripper_id" sheetId="17" r:id="rId16"/>
+    <sheet name="get_pro_gripper_io_close_angle" sheetId="18" r:id="rId17"/>
+    <sheet name="get_pro_gripper_io_open_angle" sheetId="19" r:id="rId18"/>
+    <sheet name="get_pro_gripper_mini_pressure" sheetId="20" r:id="rId19"/>
+    <sheet name="get_protection_current" sheetId="21" r:id="rId20"/>
+    <sheet name="set_pro_gripper_enabled" sheetId="22" r:id="rId21"/>
+    <sheet name="set_pro_gripper_id" sheetId="23" r:id="rId22"/>
+    <sheet name="set_pro_gripper_io_close_angle" sheetId="24" r:id="rId23"/>
+    <sheet name="set_pro_gripper_io_open_angle" sheetId="25" r:id="rId24"/>
+    <sheet name="set_pro_gripper_mini_pressure" sheetId="26" r:id="rId25"/>
+    <sheet name="set_protection_current" sheetId="27" r:id="rId26"/>
+    <sheet name="get_pro_gripper_torque" sheetId="28" r:id="rId27"/>
+    <sheet name="set_pro_gripper_speed" sheetId="29" r:id="rId28"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="102">
   <si>
     <t>ID</t>
   </si>
@@ -52,57 +65,39 @@
     <t>api</t>
   </si>
   <si>
+    <t>parameters</t>
+  </si>
+  <si>
+    <t>expect_data</t>
+  </si>
+  <si>
+    <t>正确获取固件次版本号</t>
+  </si>
+  <si>
+    <t>get_pro_gripper_modified_version</t>
+  </si>
+  <si>
+    <t>正确获取固件版本号</t>
+  </si>
+  <si>
+    <t>get_pro_gripper_firmware_version</t>
+  </si>
+  <si>
     <t>parameter</t>
   </si>
   <si>
-    <t>expect_data</t>
-  </si>
-  <si>
-    <t>正确获取夹爪参数（主版本号）</t>
+    <t>正确获取夹爪角度</t>
+  </si>
+  <si>
+    <t>get_pro_gripper_angle</t>
+  </si>
+  <si>
+    <t>正确获取夹爪速度</t>
   </si>
   <si>
     <t>get_pro_gripper</t>
   </si>
   <si>
-    <t>正确获取夹爪参数（次版本号）</t>
-  </si>
-  <si>
-    <t>正确获取夹爪参数（ID）</t>
-  </si>
-  <si>
-    <t>正确获取夹爪参数（顺时针可运行误差）</t>
-  </si>
-  <si>
-    <t>正确获取夹爪参数（逆时针可运行误差）</t>
-  </si>
-  <si>
-    <t>正确获取夹爪参数（最小启动力）</t>
-  </si>
-  <si>
-    <t>正确获取夹爪参数（IO张开角度）</t>
-  </si>
-  <si>
-    <t>正确获取夹爪参数（IO闭合角度）</t>
-  </si>
-  <si>
-    <t>正确获取夹爪参数（当前队列数量）</t>
-  </si>
-  <si>
-    <t>正确获取夹爪参数（舵机虚位数值）</t>
-  </si>
-  <si>
-    <t>正确获取夹爪参数（夹持电流）</t>
-  </si>
-  <si>
-    <t>正确获取夹爪角度</t>
-  </si>
-  <si>
-    <t>get_pro_gripper_angle</t>
-  </si>
-  <si>
-    <t>正确获取夹爪速度</t>
-  </si>
-  <si>
     <t>test_type</t>
   </si>
   <si>
@@ -250,40 +245,132 @@
     <t>set_pro_gripper_resume</t>
   </si>
   <si>
+    <t>正确设置夹爪停止运动</t>
+  </si>
+  <si>
+    <t>set_pro_gripper_stop</t>
+  </si>
+  <si>
+    <t>正确设置夹爪扭矩</t>
+  </si>
+  <si>
+    <t>set_gripper_torque</t>
+  </si>
+  <si>
+    <t>设置夹爪扭矩（超限）</t>
+  </si>
+  <si>
+    <t>正确获取夹爪ID号</t>
+  </si>
+  <si>
+    <t>get_pro_gripper_id</t>
+  </si>
+  <si>
+    <t>正确获取夹爪关闭角度</t>
+  </si>
+  <si>
+    <t>get_pro_gripper_io_close_angle</t>
+  </si>
+  <si>
+    <t>获取夹爪张开角度</t>
+  </si>
+  <si>
+    <t>get_pro_gripper_io_open_angle</t>
+  </si>
+  <si>
+    <t>正确获取夹爪最小启动力</t>
+  </si>
+  <si>
+    <t>get_pro_gripper_mini_pressure</t>
+  </si>
+  <si>
+    <t>正确获取夹爪夹持电流</t>
+  </si>
+  <si>
+    <t>get_pro_gripper_protection_current</t>
+  </si>
+  <si>
+    <t>正确设置夹爪使能状态(上使能)</t>
+  </si>
+  <si>
+    <t>set_pro_gripper_enabled</t>
+  </si>
+  <si>
+    <t>正确设置夹爪使能状态(下使能)</t>
+  </si>
+  <si>
+    <t>设置夹爪使能状态（超限）</t>
+  </si>
+  <si>
+    <t>正确设置固件ID号</t>
+  </si>
+  <si>
+    <t>set_pro_gripper_id</t>
+  </si>
+  <si>
+    <t>设置固件ID号（超限）</t>
+  </si>
+  <si>
+    <t>正确设置夹爪关闭角度</t>
+  </si>
+  <si>
+    <t>set_pro_gripper_io_close_angle</t>
+  </si>
+  <si>
+    <t>设置夹爪关闭角度（超限）</t>
+  </si>
+  <si>
+    <t>正确设置夹爪张开角度</t>
+  </si>
+  <si>
+    <t>set_pro_gripper_io_open_angle</t>
+  </si>
+  <si>
+    <t>设置夹爪张开角度（超限）</t>
+  </si>
+  <si>
+    <t>正确设置夹爪最小启动力</t>
+  </si>
+  <si>
+    <t>set_pro_gripper_mini_pressure</t>
+  </si>
+  <si>
+    <t>设置夹爪最小启动力（超限）</t>
+  </si>
+  <si>
+    <t>正确设置夹爪夹持电流</t>
+  </si>
+  <si>
+    <t>set_protection_current</t>
+  </si>
+  <si>
+    <t>设置夹爪夹持电流（超限）</t>
+  </si>
+  <si>
+    <t>正确获取夹爪扭矩</t>
+  </si>
+  <si>
+    <t>get_pro_gripper_torque</t>
+  </si>
+  <si>
     <t>正确设置夹爪速度</t>
   </si>
   <si>
-    <t>set_speed</t>
+    <t>set_pro_gripper_speed</t>
   </si>
   <si>
     <t>设置夹爪速度（超限）</t>
-  </si>
-  <si>
-    <t>正确设置夹爪停止运动</t>
-  </si>
-  <si>
-    <t>set_pro_gripper_stop</t>
-  </si>
-  <si>
-    <t>正确设置夹爪扭矩</t>
-  </si>
-  <si>
-    <t>set_gripper_torque</t>
-  </si>
-  <si>
-    <t>设置夹爪扭矩（超限）</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -895,7 +982,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1209,16 +1296,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="19.4416666666667" customWidth="1"/>
+    <col min="2" max="2" width="18.8916666666667" customWidth="1"/>
+    <col min="3" max="3" width="22.225" customWidth="1"/>
     <col min="4" max="4" width="15.5583333333333" customWidth="1"/>
-    <col min="5" max="5" width="14.775" customWidth="1"/>
+    <col min="5" max="5" width="17.5583333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" customFormat="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1235,7 +1322,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5">
+    <row r="2" customFormat="1" ht="27" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1245,181 +1332,9 @@
       <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="3" ht="27" spans="1:5">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="1">
-        <v>2</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="D2" s="1"/>
+      <c r="E2" s="1">
         <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="1">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" ht="27" spans="1:5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>22</v>
-      </c>
-      <c r="E5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" ht="27" spans="1:5">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>24</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" ht="27" spans="1:5">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <v>26</v>
-      </c>
-      <c r="E7">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="8" ht="27" spans="1:5">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8">
-        <v>34</v>
-      </c>
-      <c r="E8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" ht="27" spans="1:5">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9">
-        <v>35</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="27" spans="1:5">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10">
-        <v>40</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="27" spans="1:5">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11">
-        <v>42</v>
-      </c>
-      <c r="E11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" ht="27" spans="1:5">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12">
-        <v>44</v>
-      </c>
-      <c r="E12">
-        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -1453,7 +1368,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -1464,10 +1379,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -1486,11 +1401,14 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="1" max="1" width="13.5583333333333" customWidth="1"/>
+    <col min="2" max="2" width="27.1083333333333" customWidth="1"/>
+    <col min="3" max="3" width="24.5583333333333" customWidth="1"/>
+    <col min="4" max="4" width="13.4416666666667" customWidth="1"/>
+    <col min="5" max="5" width="13.225" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1501,21 +1419,21 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" ht="42" customHeight="1" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -1549,7 +1467,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -1560,10 +1478,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -1579,18 +1497,14 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="8.89166666666667" style="1"/>
-    <col min="2" max="2" width="21.775" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.775" style="1" customWidth="1"/>
-    <col min="4" max="5" width="8.89166666666667" style="1"/>
-    <col min="6" max="6" width="12.775" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.89166666666667" style="1"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" ht="27" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1601,67 +1515,25 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:6">
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" s="1">
-        <v>100</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="D2" s="1"/>
       <c r="E2" s="1">
         <v>1</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:6">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D3" s="1">
-        <v>101</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:6">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1691,7 +1563,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -1702,10 +1574,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -1741,13 +1613,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="28" customHeight="1" spans="1:6">
@@ -1755,10 +1627,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D2" s="1">
         <v>10</v>
@@ -1767,7 +1639,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="27" spans="1:6">
@@ -1775,16 +1647,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D3" s="1">
         <v>255</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="27" spans="1:6">
@@ -1792,16 +1664,209 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <cols>
+    <col min="2" max="2" width="18.8916666666667" customWidth="1"/>
+    <col min="3" max="3" width="22.225" customWidth="1"/>
+    <col min="5" max="5" width="17.5583333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" ht="27" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" spans="1:5">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <cols>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" ht="27" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="27" spans="1:5">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <cols>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" ht="27" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="27" spans="1:5">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <cols>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" ht="27" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="27" spans="1:5">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1814,15 +1879,59 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="5" width="19.3333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="27" spans="1:5">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="19.4416666666667" customWidth="1"/>
-    <col min="4" max="4" width="15.5583333333333" customWidth="1"/>
-    <col min="5" max="5" width="14.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" customFormat="1" ht="27" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1833,30 +1942,741 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5">
+    <row r="2" customFormat="1" ht="27" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
+        <v>300</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="8.89166666666667"/>
+    <col min="2" max="2" width="20.4416666666667" customWidth="1"/>
+    <col min="3" max="3" width="19.5583333333333" customWidth="1"/>
+    <col min="4" max="4" width="12.775" customWidth="1"/>
+    <col min="5" max="5" width="14.225" customWidth="1"/>
+    <col min="6" max="16384" width="8.89166666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="27" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="27" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="27" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" ht="27" spans="1:6">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="5" width="19.3333333333333" customWidth="1"/>
+    <col min="6" max="6" width="16.225" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="45" customHeight="1" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="1">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="27" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="27" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="1">
+        <v>255</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="6" max="6" width="11.6666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="27" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="1">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="27" spans="1:6">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3">
+        <v>-1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="27" spans="1:6">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4">
+        <v>101</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="6" max="6" width="11.6666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="27" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2" s="1">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="27" spans="1:6">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3">
+        <v>-1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="27" spans="1:6">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4">
+        <v>101</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="8.89166666666667"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="4" max="16384" width="8.89166666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="27" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="1">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="27" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="1">
+        <v>255</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="27" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="8.89166666666667"/>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="4" max="16384" width="8.89166666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" s="1">
+        <v>150</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="27" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" s="1">
+        <v>301</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="27" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="1">
+        <v>99</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <cols>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="24.775" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" ht="27" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" spans="1:5">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="8.89166666666667" style="1"/>
+    <col min="2" max="2" width="21.775" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.775" style="1" customWidth="1"/>
+    <col min="4" max="5" width="8.89166666666667" style="1"/>
+    <col min="6" max="6" width="12.775" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.89166666666667" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" s="1">
+        <v>100</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="1">
+        <v>101</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1884,7 +2704,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -1895,14 +2715,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1913,6 +2733,57 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <cols>
+    <col min="2" max="2" width="21.775" customWidth="1"/>
+    <col min="3" max="3" width="19.4416666666667" customWidth="1"/>
+    <col min="4" max="4" width="15.5583333333333" customWidth="1"/>
+    <col min="5" max="5" width="14.775" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
@@ -1937,13 +2808,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="45" customHeight="1" spans="1:6">
@@ -1951,10 +2822,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -1968,10 +2839,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
@@ -1985,10 +2856,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1">
         <v>2</v>
@@ -2002,10 +2873,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1">
         <v>3</v>
@@ -2020,7 +2891,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G29"/>
@@ -2043,16 +2914,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:7">
@@ -2060,10 +2931,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1">
         <v>10</v>
@@ -2075,7 +2946,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:7">
@@ -2083,10 +2954,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1">
         <v>10</v>
@@ -2098,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:7">
@@ -2106,10 +2977,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1">
         <v>10</v>
@@ -2118,7 +2989,7 @@
         <v>2</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:7">
@@ -2126,10 +2997,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <v>21</v>
@@ -2141,7 +3012,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:7">
@@ -2149,10 +3020,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D6">
         <v>21</v>
@@ -2160,9 +3031,8 @@
       <c r="E6">
         <v>17</v>
       </c>
-      <c r="F6"/>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:7">
@@ -2170,10 +3040,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D7">
         <v>21</v>
@@ -2182,7 +3052,7 @@
         <v>-1</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" ht="27" spans="1:7">
@@ -2190,10 +3060,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D8">
         <v>23</v>
@@ -2205,7 +3075,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:7">
@@ -2213,10 +3083,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D9">
         <v>23</v>
@@ -2224,9 +3094,8 @@
       <c r="E9">
         <v>17</v>
       </c>
-      <c r="F9"/>
       <c r="G9" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" ht="27" spans="1:7">
@@ -2234,10 +3103,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D10">
         <v>23</v>
@@ -2246,7 +3115,7 @@
         <v>-1</v>
       </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" ht="27" spans="1:7">
@@ -2254,10 +3123,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D11">
         <v>25</v>
@@ -2266,7 +3135,7 @@
         <v>120</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2274,10 +3143,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D12">
         <v>25</v>
@@ -2286,7 +3155,7 @@
         <v>255</v>
       </c>
       <c r="G12" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2294,10 +3163,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D13">
         <v>25</v>
@@ -2306,7 +3175,7 @@
         <v>-1</v>
       </c>
       <c r="G13" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" ht="27" spans="1:7">
@@ -2314,10 +3183,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D14">
         <v>29</v>
@@ -2326,7 +3195,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" ht="27" spans="1:7">
@@ -2334,10 +3203,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D15">
         <v>29</v>
@@ -2349,7 +3218,7 @@
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" ht="27" spans="1:7">
@@ -2357,10 +3226,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D16">
         <v>29</v>
@@ -2372,7 +3241,7 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" ht="27" spans="1:7">
@@ -2380,10 +3249,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D17">
         <v>29</v>
@@ -2395,7 +3264,7 @@
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2403,10 +3272,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D18">
         <v>29</v>
@@ -2415,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2423,10 +3292,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D19">
         <v>29</v>
@@ -2435,7 +3304,7 @@
         <v>18</v>
       </c>
       <c r="G19" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" ht="27" spans="1:7">
@@ -2443,10 +3312,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D20">
         <v>30</v>
@@ -2458,7 +3327,7 @@
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2466,10 +3335,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D21">
         <v>30</v>
@@ -2478,7 +3347,7 @@
         <v>101</v>
       </c>
       <c r="G21" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" ht="27" spans="1:7">
@@ -2486,10 +3355,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D22">
         <v>31</v>
@@ -2501,7 +3370,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2509,10 +3378,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D23">
         <v>31</v>
@@ -2521,7 +3390,7 @@
         <v>-1</v>
       </c>
       <c r="G23" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" ht="27" spans="1:7">
@@ -2529,10 +3398,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D24">
         <v>41</v>
@@ -2544,7 +3413,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2552,10 +3421,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D25">
         <v>41</v>
@@ -2564,7 +3433,7 @@
         <v>-1</v>
       </c>
       <c r="G25" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2572,10 +3441,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D26">
         <v>41</v>
@@ -2584,7 +3453,7 @@
         <v>101</v>
       </c>
       <c r="G26" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" ht="27" spans="1:7">
@@ -2592,10 +3461,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D27">
         <v>43</v>
@@ -2604,7 +3473,7 @@
         <v>200</v>
       </c>
       <c r="G27" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2612,10 +3481,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D28">
         <v>43</v>
@@ -2624,7 +3493,7 @@
         <v>301</v>
       </c>
       <c r="G28" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2632,10 +3501,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D29">
         <v>43</v>
@@ -2644,7 +3513,7 @@
         <v>99</v>
       </c>
       <c r="G29" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2653,7 +3522,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
@@ -2678,24 +3547,24 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="27" spans="1:6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D2" s="1">
         <v>50</v>
@@ -2712,10 +3581,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
@@ -2724,15 +3593,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="4" s="1" customFormat="1" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
@@ -2746,16 +3615,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1">
         <v>101</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2764,7 +3633,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
@@ -2789,13 +3658,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="27" spans="1:6">
@@ -2803,10 +3672,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
@@ -2815,7 +3684,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="27" spans="1:6">
@@ -2823,10 +3692,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -2835,7 +3704,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="27" spans="1:6">
@@ -2843,10 +3712,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D4" s="1">
         <v>50</v>
@@ -2855,7 +3724,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="27" spans="1:6">
@@ -2863,67 +3732,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D5" s="1">
         <v>101</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
-  <cols>
-    <col min="1" max="1" width="13.5583333333333" customWidth="1"/>
-    <col min="2" max="2" width="27.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="24.5583333333333" customWidth="1"/>
-    <col min="4" max="4" width="13.4416666666667" customWidth="1"/>
-    <col min="5" max="5" width="13.225" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" ht="42" customHeight="1" spans="1:5">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2956,7 +3774,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -2967,10 +3785,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">

--- a/test_data/pro_gripper.xlsx
+++ b/test_data/pro_gripper.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="14055" tabRatio="620" firstSheet="31" activeTab="38"/>
+    <workbookView windowWidth="29000" windowHeight="13200" tabRatio="620" firstSheet="30" activeTab="38"/>
   </bookViews>
   <sheets>
     <sheet name="get_firmware_version" sheetId="1" r:id="rId1"/>
@@ -1357,9 +1357,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
+    <col min="1" max="5" width="19.3363636363636" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1380,7 +1380,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:5">
+    <row r="2" ht="28" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="1">
-        <v>13</v>
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
@@ -1405,10 +1405,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.4416666666667" style="1" customWidth="1"/>
+    <col min="1" max="5" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.4454545454545" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1450,7 +1450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1467,7 +1467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="40.5" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="42" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="40.5" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="42" spans="1:6">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1511,13 +1511,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.5583333333333" customWidth="1"/>
-    <col min="2" max="2" width="27.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="24.5583333333333" customWidth="1"/>
-    <col min="4" max="4" width="13.4416666666667" customWidth="1"/>
-    <col min="5" max="5" width="13.225" customWidth="1"/>
+    <col min="1" max="1" width="13.5545454545455" customWidth="1"/>
+    <col min="2" max="2" width="27.1090909090909" customWidth="1"/>
+    <col min="3" max="3" width="24.5545454545455" customWidth="1"/>
+    <col min="4" max="4" width="13.4454545454545" customWidth="1"/>
+    <col min="5" max="5" width="13.2272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1562,13 +1562,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.5583333333333" customWidth="1"/>
-    <col min="2" max="2" width="27.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="24.5583333333333" customWidth="1"/>
-    <col min="4" max="4" width="13.4416666666667" customWidth="1"/>
-    <col min="5" max="5" width="13.225" customWidth="1"/>
+    <col min="1" max="1" width="13.5545454545455" customWidth="1"/>
+    <col min="2" max="2" width="27.1090909090909" customWidth="1"/>
+    <col min="3" max="3" width="24.5545454545455" customWidth="1"/>
+    <col min="4" max="4" width="13.4454545454545" customWidth="1"/>
+    <col min="5" max="5" width="13.2272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1655,13 +1655,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.5583333333333" customWidth="1"/>
-    <col min="2" max="2" width="27.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="24.5583333333333" customWidth="1"/>
-    <col min="4" max="4" width="13.4416666666667" customWidth="1"/>
-    <col min="5" max="5" width="13.225" customWidth="1"/>
+    <col min="1" max="1" width="13.5545454545455" customWidth="1"/>
+    <col min="2" max="2" width="27.1090909090909" customWidth="1"/>
+    <col min="3" max="3" width="24.5545454545455" customWidth="1"/>
+    <col min="4" max="4" width="13.4454545454545" customWidth="1"/>
+    <col min="5" max="5" width="13.2272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1748,13 +1748,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="19.4416666666667" customWidth="1"/>
+    <col min="2" max="2" width="21.7727272727273" customWidth="1"/>
+    <col min="3" max="3" width="19.4454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" ht="28" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1796,13 +1796,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.5583333333333" customWidth="1"/>
-    <col min="2" max="2" width="27.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="24.5583333333333" customWidth="1"/>
-    <col min="4" max="4" width="13.4416666666667" customWidth="1"/>
-    <col min="5" max="5" width="13.225" customWidth="1"/>
+    <col min="1" max="1" width="13.5545454545455" customWidth="1"/>
+    <col min="2" max="2" width="27.1090909090909" customWidth="1"/>
+    <col min="3" max="3" width="24.5545454545455" customWidth="1"/>
+    <col min="4" max="4" width="13.4454545454545" customWidth="1"/>
+    <col min="5" max="5" width="13.2272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1889,13 +1889,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="19.4416666666667" customWidth="1"/>
+    <col min="2" max="2" width="21.7727272727273" customWidth="1"/>
+    <col min="3" max="3" width="19.4454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" ht="28" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1937,13 +1937,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="19.4416666666667" customWidth="1"/>
+    <col min="2" max="2" width="21.7727272727273" customWidth="1"/>
+    <col min="3" max="3" width="19.4454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" ht="28" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:5">
+    <row r="2" ht="28" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1985,13 +1985,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="19.4416666666667" customWidth="1"/>
+    <col min="2" max="2" width="21.7727272727273" customWidth="1"/>
+    <col min="3" max="3" width="19.4454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:6">
+    <row r="1" ht="28" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:6">
+    <row r="2" ht="28" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="27" spans="1:6">
+    <row r="3" ht="28" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:6">
+    <row r="4" ht="28" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2075,13 +2075,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="19.4416666666667" customWidth="1"/>
+    <col min="2" max="2" width="21.7727272727273" customWidth="1"/>
+    <col min="3" max="3" width="19.4454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:6">
+    <row r="1" ht="28" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:6">
+    <row r="2" ht="28" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2121,7 +2121,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="27" spans="1:6">
+    <row r="3" ht="28" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:6">
+    <row r="4" ht="28" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2165,14 +2165,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="18.8916666666667" customWidth="1"/>
-    <col min="3" max="3" width="22.225" customWidth="1"/>
-    <col min="5" max="5" width="17.5583333333333" customWidth="1"/>
+    <col min="2" max="2" width="18.8909090909091" customWidth="1"/>
+    <col min="3" max="3" width="22.2272727272727" customWidth="1"/>
+    <col min="5" max="5" width="17.5545454545455" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" ht="28" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:5">
+    <row r="2" ht="28" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2215,13 +2215,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="19.4416666666667" customWidth="1"/>
+    <col min="2" max="2" width="21.7727272727273" customWidth="1"/>
+    <col min="3" max="3" width="19.4454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" ht="28" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2238,7 +2238,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:5">
+    <row r="2" ht="28" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2263,15 +2263,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.89166666666667" style="1"/>
-    <col min="2" max="2" width="21.775" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.775" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.89166666666667" style="1"/>
+    <col min="1" max="1" width="8.89090909090909" style="1"/>
+    <col min="2" max="2" width="21.7727272727273" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7727272727273" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.89090909090909" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:6">
+    <row r="1" ht="28" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" ht="28" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="27" spans="1:6">
+    <row r="3" ht="28" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:6">
+    <row r="4" ht="28" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2355,13 +2355,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7727272727273" customWidth="1"/>
+    <col min="3" max="3" width="24.7727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" ht="28" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" ht="28" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2403,15 +2403,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.89166666666667" style="1"/>
-    <col min="2" max="2" width="21.775" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.775" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.89166666666667" style="1"/>
+    <col min="1" max="1" width="8.89090909090909" style="1"/>
+    <col min="2" max="2" width="21.7727272727273" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7727272727273" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.89090909090909" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2495,13 +2495,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7727272727273" customWidth="1"/>
+    <col min="3" max="3" width="24.7727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" ht="28" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2543,14 +2543,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
-    <col min="6" max="6" width="11.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="21.7727272727273" customWidth="1"/>
+    <col min="3" max="3" width="24.7727272727273" customWidth="1"/>
+    <col min="6" max="6" width="11.6636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:6">
+    <row r="1" ht="28" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2694,14 +2694,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
-    <col min="6" max="6" width="11.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="21.7727272727273" customWidth="1"/>
+    <col min="3" max="3" width="24.7727272727273" customWidth="1"/>
+    <col min="6" max="6" width="11.6636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:6">
+    <row r="1" ht="28" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="27" spans="1:6">
+    <row r="3" customFormat="1" ht="28" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="27" spans="1:6">
+    <row r="4" customFormat="1" ht="28" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2785,14 +2785,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
-    <col min="6" max="6" width="11.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="21.7727272727273" customWidth="1"/>
+    <col min="3" max="3" width="24.7727272727273" customWidth="1"/>
+    <col min="6" max="6" width="11.6636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:6">
+    <row r="1" ht="28" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="27" spans="1:6">
+    <row r="3" ht="28" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:6">
+    <row r="4" ht="28" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2876,17 +2876,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.89166666666667" style="1"/>
-    <col min="2" max="2" width="21.775" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.775" style="1" customWidth="1"/>
-    <col min="4" max="5" width="8.89166666666667" style="1"/>
-    <col min="6" max="6" width="12.775" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.89166666666667" style="1"/>
+    <col min="1" max="1" width="8.89090909090909" style="1"/>
+    <col min="2" max="2" width="21.7727272727273" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7727272727273" style="1" customWidth="1"/>
+    <col min="4" max="5" width="8.89090909090909" style="1"/>
+    <col min="6" max="6" width="12.7727272727273" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.89090909090909" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:6">
+    <row r="1" ht="28" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2970,13 +2970,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7727272727273" customWidth="1"/>
+    <col min="3" max="3" width="24.7727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" ht="28" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3018,14 +3018,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="18.8916666666667" customWidth="1"/>
-    <col min="3" max="3" width="22.225" customWidth="1"/>
-    <col min="5" max="5" width="17.5583333333333" customWidth="1"/>
+    <col min="2" max="2" width="18.8909090909091" customWidth="1"/>
+    <col min="3" max="3" width="22.2272727272727" customWidth="1"/>
+    <col min="5" max="5" width="17.5545454545455" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" ht="28" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3068,13 +3068,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7727272727273" customWidth="1"/>
+    <col min="3" max="3" width="24.7727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" ht="28" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3116,13 +3116,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7727272727273" customWidth="1"/>
+    <col min="3" max="3" width="24.7727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" ht="28" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3164,17 +3164,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="8.89166666666667" style="1"/>
-    <col min="2" max="2" width="21.775" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.775" style="1" customWidth="1"/>
-    <col min="4" max="6" width="8.89166666666667" style="1"/>
-    <col min="7" max="7" width="12.6666666666667" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.89166666666667" style="1"/>
+    <col min="1" max="1" width="8.89090909090909" style="1"/>
+    <col min="2" max="2" width="21.7727272727273" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7727272727273" style="1" customWidth="1"/>
+    <col min="4" max="6" width="8.89090909090909" style="1"/>
+    <col min="7" max="7" width="12.6636363636364" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.89090909090909" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:7">
+    <row r="1" ht="28" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3217,7 +3217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="27" spans="1:7">
+    <row r="3" ht="28" spans="1:7">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="27" spans="1:7">
+    <row r="5" ht="28" spans="1:7">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -3271,7 +3271,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" ht="27" spans="1:7">
+    <row r="6" ht="28" spans="1:7">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -3301,13 +3301,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7727272727273" customWidth="1"/>
+    <col min="3" max="3" width="24.7727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" ht="28" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3349,13 +3349,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7727272727273" customWidth="1"/>
+    <col min="3" max="3" width="24.7727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" ht="28" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3397,13 +3397,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7727272727273" customWidth="1"/>
+    <col min="3" max="3" width="24.7727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" ht="28" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3445,13 +3445,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7727272727273" customWidth="1"/>
+    <col min="3" max="3" width="24.7727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" ht="28" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3493,15 +3493,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.89166666666667" style="1"/>
-    <col min="2" max="2" width="21.775" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.775" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.89166666666667" style="1"/>
+    <col min="1" max="1" width="8.89090909090909" style="1"/>
+    <col min="2" max="2" width="21.7727272727273" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7727272727273" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.89090909090909" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:6">
+    <row r="1" ht="28" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="27" spans="1:6">
+    <row r="3" ht="28" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:6">
+    <row r="4" ht="28" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3585,13 +3585,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7727272727273" customWidth="1"/>
+    <col min="3" max="3" width="24.7727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" ht="28" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3633,15 +3633,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.89166666666667" style="1"/>
-    <col min="2" max="2" width="21.775" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.775" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.89166666666667" style="1"/>
+    <col min="1" max="1" width="8.89090909090909" style="1"/>
+    <col min="2" max="2" width="21.7727272727273" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7727272727273" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.89090909090909" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:6">
+    <row r="1" ht="28" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>114</v>
       </c>
       <c r="D2" s="1">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="27" spans="1:6">
+    <row r="3" ht="28" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3698,7 +3698,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:6">
+    <row r="4" ht="28" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3725,10 +3725,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.225" style="1" customWidth="1"/>
+    <col min="1" max="5" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.2272727272727" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -3772,7 +3772,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="27" spans="1:6">
+    <row r="3" ht="28" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3789,7 +3789,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:6">
+    <row r="4" ht="28" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3816,13 +3816,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7727272727273" customWidth="1"/>
+    <col min="3" max="3" width="24.7727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" ht="28" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3864,11 +3864,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="22.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="22.6636363636364" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="5" max="5" width="12.8916666666667" customWidth="1"/>
+    <col min="5" max="5" width="12.8909090909091" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3913,10 +3913,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.225" style="1" customWidth="1"/>
+    <col min="1" max="5" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.2272727272727" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4004,17 +4004,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.89166666666667" style="1"/>
-    <col min="2" max="2" width="20.4416666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.5583333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.775" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.225" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.89166666666667" style="1"/>
+    <col min="1" max="1" width="8.89090909090909" style="1"/>
+    <col min="2" max="2" width="20.4454545454545" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5545454545455" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7727272727273" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.2272727272727" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.89090909090909" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:6">
+    <row r="1" ht="28" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:6">
+    <row r="2" ht="28" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -4054,7 +4054,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="27" spans="1:6">
+    <row r="3" ht="28" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -4074,7 +4074,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:6">
+    <row r="4" ht="28" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -4091,7 +4091,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="27" spans="1:6">
+    <row r="5" ht="28" spans="1:6">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -4118,17 +4118,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.5583333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.1083333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.8916666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.4416666666667" style="1" customWidth="1"/>
-    <col min="5" max="6" width="13.225" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.89166666666667" style="1"/>
+    <col min="1" max="1" width="13.5545454545455" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.1090909090909" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.8909090909091" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.4454545454545" style="1" customWidth="1"/>
+    <col min="5" max="6" width="13.2272727272727" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.89090909090909" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:7">
+    <row r="1" ht="28" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4197,7 +4197,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:7">
+    <row r="4" ht="28" spans="1:7">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -4217,7 +4217,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="27" spans="1:7">
+    <row r="5" ht="28" spans="1:7">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -4247,13 +4247,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.5583333333333" customWidth="1"/>
-    <col min="2" max="2" width="27.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="24.5583333333333" customWidth="1"/>
-    <col min="4" max="4" width="13.4416666666667" customWidth="1"/>
-    <col min="5" max="5" width="13.225" customWidth="1"/>
+    <col min="1" max="1" width="13.5545454545455" customWidth="1"/>
+    <col min="2" max="2" width="27.1090909090909" customWidth="1"/>
+    <col min="3" max="3" width="24.5545454545455" customWidth="1"/>
+    <col min="4" max="4" width="13.4454545454545" customWidth="1"/>
+    <col min="5" max="5" width="13.2272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">

--- a/test_data/pro_gripper.xlsx
+++ b/test_data/pro_gripper.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" firstSheet="23" activeTab="24"/>
+    <workbookView windowWidth="27948" windowHeight="12300" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="get_modified_version" sheetId="1" r:id="rId1"/>
@@ -1297,12 +1297,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="18.8916666666667" customWidth="1"/>
-    <col min="3" max="3" width="22.225" customWidth="1"/>
-    <col min="4" max="4" width="15.5583333333333" customWidth="1"/>
-    <col min="5" max="5" width="17.5583333333333" customWidth="1"/>
+    <col min="2" max="2" width="18.8888888888889" customWidth="1"/>
+    <col min="3" max="3" width="22.2222222222222" customWidth="1"/>
+    <col min="4" max="4" width="15.5555555555556" customWidth="1"/>
+    <col min="5" max="5" width="17.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" spans="1:5">
@@ -1322,7 +1322,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="27" spans="1:5">
+    <row r="2" customFormat="1" ht="28.8" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1348,13 +1348,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.5583333333333" customWidth="1"/>
-    <col min="2" max="2" width="27.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="24.5583333333333" customWidth="1"/>
-    <col min="4" max="4" width="13.4416666666667" customWidth="1"/>
-    <col min="5" max="5" width="13.225" customWidth="1"/>
+    <col min="1" max="1" width="13.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="27.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="24.5555555555556" customWidth="1"/>
+    <col min="4" max="4" width="13.4444444444444" customWidth="1"/>
+    <col min="5" max="5" width="13.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1399,13 +1399,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.5583333333333" customWidth="1"/>
-    <col min="2" max="2" width="27.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="24.5583333333333" customWidth="1"/>
-    <col min="4" max="4" width="13.4416666666667" customWidth="1"/>
-    <col min="5" max="5" width="13.225" customWidth="1"/>
+    <col min="1" max="1" width="13.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="27.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="24.5555555555556" customWidth="1"/>
+    <col min="4" max="4" width="13.4444444444444" customWidth="1"/>
+    <col min="5" max="5" width="13.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1450,13 +1450,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" ht="28.8" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1498,13 +1498,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" ht="28.8" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1546,13 +1546,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" ht="28.8" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1594,15 +1594,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.89166666666667" style="1"/>
-    <col min="2" max="2" width="21.775" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.775" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.89166666666667" style="1"/>
+    <col min="1" max="1" width="8.88888888888889" style="1"/>
+    <col min="2" max="2" width="21.7777777777778" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7777777777778" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1686,14 +1686,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="18.8916666666667" customWidth="1"/>
-    <col min="3" max="3" width="22.225" customWidth="1"/>
-    <col min="5" max="5" width="17.5583333333333" customWidth="1"/>
+    <col min="2" max="2" width="18.8888888888889" customWidth="1"/>
+    <col min="3" max="3" width="22.2222222222222" customWidth="1"/>
+    <col min="5" max="5" width="17.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="27" spans="1:5">
+    <row r="1" customFormat="1" ht="28.8" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1735,13 +1735,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="27" spans="1:5">
+    <row r="1" customFormat="1" ht="28.8" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="27" spans="1:5">
+    <row r="2" customFormat="1" ht="28.8" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1783,13 +1783,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="27" spans="1:5">
+    <row r="1" customFormat="1" ht="28.8" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="27" spans="1:5">
+    <row r="2" customFormat="1" ht="28.8" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1831,13 +1831,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="27" spans="1:5">
+    <row r="1" customFormat="1" ht="28.8" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="27" spans="1:5">
+    <row r="2" customFormat="1" ht="28.8" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1879,7 +1879,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="5" width="19.3333333333333" customWidth="1"/>
   </cols>
@@ -1901,7 +1901,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="27" spans="1:5">
+    <row r="2" customFormat="1" ht="28.8" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="1">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
@@ -1925,13 +1925,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="27" spans="1:5">
+    <row r="1" customFormat="1" ht="28.8" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="27" spans="1:5">
+    <row r="2" customFormat="1" ht="28.8" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1973,17 +1973,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.89166666666667"/>
-    <col min="2" max="2" width="20.4416666666667" customWidth="1"/>
-    <col min="3" max="3" width="19.5583333333333" customWidth="1"/>
-    <col min="4" max="4" width="12.775" customWidth="1"/>
-    <col min="5" max="5" width="14.225" customWidth="1"/>
-    <col min="6" max="16384" width="8.89166666666667"/>
+    <col min="1" max="1" width="8.88888888888889"/>
+    <col min="2" max="2" width="20.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="19.5555555555556" customWidth="1"/>
+    <col min="4" max="4" width="12.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="14.2222222222222" customWidth="1"/>
+    <col min="6" max="16384" width="8.88888888888889"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="27" spans="1:6">
+    <row r="2" customFormat="1" ht="28.8" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2023,7 +2023,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="27" spans="1:6">
+    <row r="3" customFormat="1" ht="28.8" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2043,7 +2043,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="27" spans="1:6">
+    <row r="4" customFormat="1" ht="28.8" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" customFormat="1" ht="27" spans="1:6">
+    <row r="5" customFormat="1" ht="28.8" spans="1:6">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2087,10 +2087,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="5" width="19.3333333333333" customWidth="1"/>
-    <col min="6" max="6" width="16.225" customWidth="1"/>
+    <col min="6" max="6" width="16.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -2133,7 +2133,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="27" spans="1:6">
+    <row r="3" customFormat="1" ht="28.8" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2150,7 +2150,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="27" spans="1:6">
+    <row r="4" customFormat="1" ht="28.8" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2177,14 +2177,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
     <col min="6" max="6" width="11.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="27" spans="1:6">
+    <row r="2" customFormat="1" ht="28.8" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2224,7 +2224,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="27" spans="1:6">
+    <row r="3" customFormat="1" ht="28.8" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="27" spans="1:6">
+    <row r="4" customFormat="1" ht="28.8" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2268,14 +2268,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
     <col min="6" max="6" width="11.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2295,7 +2295,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="27" spans="1:6">
+    <row r="2" customFormat="1" ht="28.8" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="27" spans="1:6">
+    <row r="3" customFormat="1" ht="28.8" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="27" spans="1:6">
+    <row r="4" customFormat="1" ht="28.8" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2359,15 +2359,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.89166666666667"/>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
-    <col min="4" max="16384" width="8.89166666666667"/>
+    <col min="1" max="1" width="8.88888888888889"/>
+    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
+    <col min="4" max="16384" width="8.88888888888889"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="27" spans="1:6">
+    <row r="2" customFormat="1" ht="28.8" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="27" spans="1:6">
+    <row r="3" customFormat="1" ht="28.8" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="27" spans="1:6">
+    <row r="4" customFormat="1" ht="28.8" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2451,15 +2451,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.89166666666667"/>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
-    <col min="4" max="16384" width="8.89166666666667"/>
+    <col min="1" max="1" width="8.88888888888889"/>
+    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
+    <col min="4" max="16384" width="8.88888888888889"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2499,7 +2499,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="27" spans="1:6">
+    <row r="3" customFormat="1" ht="28.8" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="27" spans="1:6">
+    <row r="4" customFormat="1" ht="28.8" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2543,13 +2543,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="24.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="24.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="27" spans="1:5">
+    <row r="1" customFormat="1" ht="28.8" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2591,17 +2591,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.89166666666667" style="1"/>
-    <col min="2" max="2" width="21.775" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.775" style="1" customWidth="1"/>
-    <col min="4" max="5" width="8.89166666666667" style="1"/>
-    <col min="6" max="6" width="12.775" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.89166666666667" style="1"/>
+    <col min="1" max="1" width="8.88888888888889" style="1"/>
+    <col min="2" max="2" width="21.7777777777778" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7777777777778" style="1" customWidth="1"/>
+    <col min="4" max="5" width="8.88888888888889" style="1"/>
+    <col min="6" max="6" width="12.7777777777778" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2685,12 +2685,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="19.4416666666667" customWidth="1"/>
-    <col min="4" max="4" width="15.5583333333333" customWidth="1"/>
-    <col min="5" max="5" width="14.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="19.4444444444444" customWidth="1"/>
+    <col min="4" max="4" width="15.5555555555556" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2736,12 +2736,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="19.4416666666667" customWidth="1"/>
-    <col min="4" max="4" width="15.5583333333333" customWidth="1"/>
-    <col min="5" max="5" width="14.775" customWidth="1"/>
+    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="19.4444444444444" customWidth="1"/>
+    <col min="4" max="4" width="15.5555555555556" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2787,13 +2787,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.4416666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.775" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.4444444444444" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7777777777778" style="1" customWidth="1"/>
     <col min="4" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.4416666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.4444444444444" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2834,7 +2834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2895,12 +2895,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="21.775" customWidth="1"/>
-    <col min="3" max="3" width="19.4416666666667" customWidth="1"/>
-    <col min="4" max="4" width="14.5583333333333" customWidth="1"/>
-    <col min="5" max="6" width="15.5583333333333" customWidth="1"/>
+    <col min="2" max="2" width="21.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="19.4444444444444" customWidth="1"/>
+    <col min="4" max="4" width="14.5555555555556" customWidth="1"/>
+    <col min="5" max="6" width="15.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3035,7 +3035,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" ht="27" spans="1:7">
+    <row r="7" ht="28.8" spans="1:7">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" ht="27" spans="1:7">
+    <row r="8" ht="28.8" spans="1:7">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" ht="27" spans="1:7">
+    <row r="9" ht="28.8" spans="1:7">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" ht="27" spans="1:7">
+    <row r="10" ht="28.8" spans="1:7">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" ht="27" spans="1:7">
+    <row r="11" ht="28.8" spans="1:7">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" ht="27" spans="1:7">
+    <row r="14" ht="28.8" spans="1:7">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" ht="27" spans="1:7">
+    <row r="15" ht="28.8" spans="1:7">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" ht="27" spans="1:7">
+    <row r="16" ht="28.8" spans="1:7">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3244,7 +3244,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" ht="27" spans="1:7">
+    <row r="17" ht="28.8" spans="1:7">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" ht="27" spans="1:7">
+    <row r="20" ht="28.8" spans="1:7">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -3350,7 +3350,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" ht="27" spans="1:7">
+    <row r="22" ht="28.8" spans="1:7">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" ht="27" spans="1:7">
+    <row r="24" ht="28.8" spans="1:7">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3456,7 +3456,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" ht="27" spans="1:7">
+    <row r="27" ht="28.8" spans="1:7">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3526,17 +3526,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.89166666666667" style="1"/>
-    <col min="2" max="2" width="21.775" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.625" style="1" customWidth="1"/>
-    <col min="4" max="5" width="8.89166666666667" style="1"/>
+    <col min="1" max="1" width="8.88888888888889" style="1"/>
+    <col min="2" max="2" width="21.7777777777778" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6296296296296" style="1" customWidth="1"/>
+    <col min="4" max="5" width="8.88888888888889" style="1"/>
     <col min="6" max="6" width="12.6666666666667" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.89166666666667" style="1"/>
+    <col min="7" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3576,7 +3576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3610,7 +3610,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -3637,17 +3637,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.5583333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.1083333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.8916666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.4416666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.225" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.89166666666667" style="1"/>
+    <col min="1" max="1" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.1111111111111" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.8888888888889" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.4444444444444" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.2222222222222" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="2" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3687,7 +3687,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -3754,13 +3754,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.5583333333333" customWidth="1"/>
-    <col min="2" max="2" width="27.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="24.5583333333333" customWidth="1"/>
-    <col min="4" max="4" width="13.4416666666667" customWidth="1"/>
-    <col min="5" max="5" width="13.225" customWidth="1"/>
+    <col min="1" max="1" width="13.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="27.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="24.5555555555556" customWidth="1"/>
+    <col min="4" max="4" width="13.4444444444444" customWidth="1"/>
+    <col min="5" max="5" width="13.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
